--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -110,7 +110,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_16-18-03</t>
+    <t>2026-09-29_16-20-26</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -110,7 +110,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_16-20-26</t>
+    <t>2026-09-29_16-24-19</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -110,7 +110,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_16-24-19</t>
+    <t>2026-09-29_16-28-24</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -110,7 +110,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_16-28-24</t>
+    <t>2026-09-29_16-45-12</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -110,7 +110,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_16-45-12</t>
+    <t>2026-09-29_16-56-16</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -110,7 +110,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_16-56-16</t>
+    <t>2026-09-29_17-02-10</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -110,7 +110,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_17-02-10</t>
+    <t>2026-09-29_20-14-46</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>Row</t>
   </si>
@@ -56,7 +56,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>C1</t>
+    <t>C1 C2 C3</t>
   </si>
   <si>
     <t>10n</t>
@@ -65,6 +65,9 @@
     <t>CP_Elec_5x5.9</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -74,13 +77,25 @@
     <t>2</t>
   </si>
   <si>
+    <t>Generic connector, single row, 01x03, script generated</t>
+  </si>
+  <si>
+    <t>Conn_01x03_Pin</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>PinSocket_1x03_P2.54mm_Vertical</t>
+  </si>
+  <si>
     <t>Resistor</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>R1</t>
+    <t>R1 R2 R3</t>
   </si>
   <si>
     <t>10k</t>
@@ -110,7 +125,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_20-14-46</t>
+    <t>2026-09-29_20-21-43</t>
   </si>
   <si>
     <t>KiCad Version:</t>
@@ -643,15 +658,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="59.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" customWidth="1"/>
+    <col min="6" max="6" width="36.7109375" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" customWidth="1"/>
@@ -659,7 +674,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -670,55 +685,55 @@
     </row>
     <row r="2" spans="1:9">
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F3" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="C4" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F4" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -726,16 +741,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F6" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -787,30 +802,30 @@
         <v>14</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>21</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>22</v>
@@ -819,10 +834,39 @@
         <v>9</v>
       </c>
       <c r="H10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="B11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>16</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -845,27 +889,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -125,7 +125,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_20-21-43</t>
+    <t>2026-09-29_20-33-24</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
   <si>
     <t>Row</t>
   </si>
@@ -122,10 +122,13 @@
     <t>Revision:</t>
   </si>
   <si>
+    <t>0.0.1</t>
+  </si>
+  <si>
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-29_20-33-24</t>
+    <t>2026-09-30</t>
   </si>
   <si>
     <t>KiCad Version:</t>
@@ -691,7 +694,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3">
         <v>3</v>
@@ -705,7 +708,7 @@
         <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3">
         <v>7</v>
@@ -716,10 +719,10 @@
         <v>33</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" s="3">
         <v>7</v>
@@ -727,13 +730,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -741,13 +744,13 @@
     </row>
     <row r="6" spans="1:9">
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" s="3">
         <v>7</v>
@@ -889,27 +892,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>Row</t>
   </si>
@@ -47,6 +47,9 @@
     <t>Datasheet</t>
   </si>
   <si>
+    <t>Sim.Pins</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -77,6 +80,21 @@
     <t>2</t>
   </si>
   <si>
+    <t>Light emitting diode</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>LED_D1.8mm_W3.3mm_H2.4mm</t>
+  </si>
+  <si>
+    <t>1=K 2=A</t>
+  </si>
+  <si>
     <t>Generic connector, single row, 01x03, script generated</t>
   </si>
   <si>
@@ -89,6 +107,9 @@
     <t>PinSocket_1x03_P2.54mm_Vertical</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>Resistor</t>
   </si>
   <si>
@@ -102,6 +123,15 @@
   </si>
   <si>
     <t>R_01005_0402Metric</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>R4 R5</t>
+  </si>
+  <si>
+    <t>R_Axial_DIN0414_L11.9mm_D4.5mm_P5.08mm_Vertical</t>
   </si>
   <si>
     <t>KiBot Bill of Materials</t>
@@ -661,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -669,15 +699,16 @@
     <col min="3" max="3" width="19.7109375" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="36.7109375" customWidth="1"/>
+    <col min="6" max="6" width="52.7109375" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32" customHeight="1">
+    <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -685,78 +716,79 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="C2" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="C5" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
@@ -784,97 +816,173 @@
       <c r="I8" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="H10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="B11" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>17</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
@@ -892,27 +1000,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -8,17 +8,19 @@
   </bookViews>
   <sheets>
     <sheet name="BoM" sheetId="1" r:id="rId1"/>
-    <sheet name="Colors" sheetId="2" r:id="rId2"/>
+    <sheet name="DNF" sheetId="2" r:id="rId2"/>
+    <sheet name="Colors" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">BoM!$9:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">DNF!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="63">
   <si>
     <t>Row</t>
   </si>
@@ -59,7 +61,7 @@
     <t>C</t>
   </si>
   <si>
-    <t>C1 C2 C3</t>
+    <t>C1 C3 C4</t>
   </si>
   <si>
     <t>10n</t>
@@ -86,7 +88,7 @@
     <t>LED</t>
   </si>
   <si>
-    <t>D1</t>
+    <t>D1 D2</t>
   </si>
   <si>
     <t>LED_D1.8mm_W3.3mm_H2.4mm</t>
@@ -116,7 +118,7 @@
     <t>R</t>
   </si>
   <si>
-    <t>R1 R2 R3</t>
+    <t>R1 R2 R3 R8</t>
   </si>
   <si>
     <t>10k</t>
@@ -128,7 +130,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>R4 R5</t>
+    <t>R4 R9</t>
   </si>
   <si>
     <t>R_Axial_DIN0414_L11.9mm_D4.5mm_P5.08mm_Vertical</t>
@@ -180,6 +182,18 @@
   </si>
   <si>
     <t>Total Components:</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (DNF)</t>
+  </si>
+  <si>
+    <t>R5 R10</t>
+  </si>
+  <si>
+    <t>R6 R7</t>
   </si>
   <si>
     <t>Columns colors</t>
@@ -355,6 +369,58 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1464384</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123779</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+            <a:ext uri="{C183D7F6-B498-43B3-948B-1728B52AA6E4}">
+              <adec:decorative xmlns:adec="http://schemas.microsoft.com/office/drawing/2017/decorative" val="1"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2378784" cy="1285829"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -729,7 +795,7 @@
         <v>49</v>
       </c>
       <c r="F2" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -743,7 +809,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -757,7 +823,7 @@
         <v>51</v>
       </c>
       <c r="F4" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -785,7 +851,7 @@
         <v>53</v>
       </c>
       <c r="F6" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -872,7 +938,7 @@
         <v>23</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>17</v>
@@ -936,7 +1002,7 @@
         <v>34</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>17</v>
@@ -992,6 +1058,243 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="52.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="52.7109375" customWidth="1"/>
+    <col min="7" max="7" width="26.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="32" customHeight="1">
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="C3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1000,27 +1303,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -130,7 +130,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>R4 R9</t>
+    <t>R9 R10</t>
   </si>
   <si>
     <t>R_Axial_DIN0414_L11.9mm_D4.5mm_P5.08mm_Vertical</t>
@@ -190,7 +190,7 @@
     <t xml:space="preserve"> (DNF)</t>
   </si>
   <si>
-    <t>R5 R10</t>
+    <t>R4 R5</t>
   </si>
   <si>
     <t>R6 R7</t>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="146">
   <si>
     <t>Row</t>
   </si>
@@ -61,6 +61,159 @@
     <t>C</t>
   </si>
   <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>1p</t>
+  </si>
+  <si>
+    <t>C_0603_1608Metric_Pad1.08x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>2p</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>3p</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>4p</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>5p</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>6p</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>7p</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>8p</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>9p</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>10p</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>11p</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>12p</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>13p</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>14p</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>15p</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>16p</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>C1 C3 C4</t>
   </si>
   <si>
@@ -70,16 +223,7 @@
     <t>CP_Elec_5x5.9</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2</t>
+    <t>18</t>
   </si>
   <si>
     <t>Light emitting diode</t>
@@ -97,6 +241,9 @@
     <t>1=K 2=A</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>Generic connector, single row, 01x03, script generated</t>
   </si>
   <si>
@@ -109,7 +256,7 @@
     <t>PinSocket_1x03_P2.54mm_Vertical</t>
   </si>
   <si>
-    <t>4</t>
+    <t>20</t>
   </si>
   <si>
     <t>Resistor</t>
@@ -118,7 +265,91 @@
     <t>R</t>
   </si>
   <si>
-    <t>R1 R2 R3 R8</t>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t>R_0805_2012Metric_Pad1.20x1.40mm_HandSolder</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>2k2</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>3k3</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>4k7</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>5k1</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>5k6</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>6k8</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>7k5</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>9k1</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R1 R2 R3</t>
   </si>
   <si>
     <t>10k</t>
@@ -127,7 +358,7 @@
     <t>R_01005_0402Metric</t>
   </si>
   <si>
-    <t>5</t>
+    <t>30</t>
   </si>
   <si>
     <t>R9 R10</t>
@@ -136,6 +367,24 @@
     <t>R_Axial_DIN0414_L11.9mm_D4.5mm_P5.08mm_Vertical</t>
   </si>
   <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>STMicroelectronics Arm Cortex-M33 MCU, 512KB flash, 96KB RAM, 100 MHz, 1.71-3.6V, 20 GPIO, WLCSP41</t>
+  </si>
+  <si>
+    <t>STM32WBA55HEFx</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>ST_WLCSP-41_2.98x2.76mm_Layout13x7_P0.4mm_Stagger</t>
+  </si>
+  <si>
+    <t>https://www.st.com/resource/en/datasheet/stm32wba55he.pdf</t>
+  </si>
+  <si>
     <t>KiBot Bill of Materials</t>
   </si>
   <si>
@@ -193,7 +442,7 @@
     <t>R4 R5</t>
   </si>
   <si>
-    <t>R6 R7</t>
+    <t>R6 R7 R8</t>
   </si>
   <si>
     <t>Columns colors</t>
@@ -757,24 +1006,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="59.7109375" customWidth="1"/>
+    <col min="2" max="2" width="60.7109375" customWidth="1"/>
     <col min="3" max="3" width="19.7109375" customWidth="1"/>
     <col min="4" max="4" width="52.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="52.7109375" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" customWidth="1"/>
     <col min="7" max="7" width="26.7109375" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="60.7109375" customWidth="1"/>
     <col min="10" max="10" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -786,55 +1035,55 @@
     </row>
     <row r="2" spans="1:10">
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="F2" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="F3" s="3">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="F4" s="3">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -842,16 +1091,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="F6" s="3">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -906,144 +1155,976 @@
         <v>15</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>21</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="F15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="B16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="8" t="s">
+      <c r="E16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="H26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G38" s="9" t="s">
         <v>18</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="30" customHeight="1">
+      <c r="A39" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1075,7 +2156,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>121</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1087,55 +2168,55 @@
     </row>
     <row r="2" spans="1:10">
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="F2" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="F3" s="3">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="F4" s="3">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1143,16 +2224,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="F6" s="3">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1198,89 +2279,89 @@
         <v>12</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1303,27 +2384,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="8" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/output/bom/ktest-bom.xlsx
+++ b/output/bom/ktest-bom.xlsx
@@ -409,7 +409,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-09-30</t>
+    <t>2026/09/30</t>
   </si>
   <si>
     <t>KiCad Version:</t>
